--- a/25-10-2026/PAT_Berth_Window.xlsx
+++ b/25-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -733,13 +742,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46320.25</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46320.625</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46321.66666666666</v>
       </c>
       <c r="G4" s="24">
@@ -771,13 +780,13 @@
       <c r="C5" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46292.20833333334</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46292.20833333334</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46293.54166666666</v>
       </c>
       <c r="G5" s="24">
@@ -809,13 +818,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46320.25</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46320.58333333334</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46321.5</v>
       </c>
       <c r="G6" s="24">
@@ -847,13 +856,13 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46321.75</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46292.16666666666</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46293.20833333334</v>
       </c>
       <c r="G7" s="24">
@@ -885,13 +894,13 @@
       <c r="C8" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46318.70833333334</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46319.625</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46321.125</v>
       </c>
       <c r="G8" s="24">
@@ -923,13 +932,13 @@
       <c r="C9" s="23" t="n">
         <v>561</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="43" t="n">
         <v>46321.625</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="43" t="n">
         <v>46321.625</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="43" t="n">
         <v>46293.125</v>
       </c>
       <c r="G9" s="24">
@@ -961,13 +970,13 @@
       <c r="C10" s="23" t="n">
         <v>449</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46293.125</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="43" t="n">
         <v>46293.20833333334</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="43" t="n">
         <v>46294.25</v>
       </c>
       <c r="G10" s="24">
@@ -999,13 +1008,13 @@
       <c r="C11" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46320.25</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>46320.25</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>46321.54166666666</v>
       </c>
       <c r="G11" s="24">
@@ -1037,13 +1046,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46292.625</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46292.625</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46294.16666666666</v>
       </c>
       <c r="G12" s="24">
@@ -1075,13 +1084,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46320.41666666666</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46320.54166666666</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46321.5</v>
       </c>
       <c r="G13" s="24">
@@ -1113,13 +1122,13 @@
       <c r="C14" s="23" t="n">
         <v>554</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46292.125</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46292.20833333334</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46293.58333333334</v>
       </c>
       <c r="G14" s="24">
@@ -1151,13 +1160,13 @@
       <c r="C15" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46320.58333333334</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46320.625</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46292.16666666666</v>
       </c>
       <c r="G15" s="24">
@@ -1189,13 +1198,13 @@
       <c r="C16" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46292.66666666666</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="43" t="n">
         <v>46292.66666666666</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="43" t="n">
         <v>46294.16666666666</v>
       </c>
       <c r="G16" s="24">
@@ -1214,7 +1223,7 @@
       <c r="J16" s="23" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1247,13 +1256,13 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G20" s="35" t="n"/>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="35" t="n"/>
-      <c r="J20" s="36" t="n"/>
+      <c r="G20" s="38" t="n"/>
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="42" t="inlineStr">
         <is>
           <t>No notices on this sheet</t>
         </is>
